--- a/forms/trg/Formulir_TRG_nifodi.xlsx
+++ b/forms/trg/Formulir_TRG_nifodi.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!F5:F30)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,14 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Andi Prastiyo, S.Hut., M.Hut.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Faculty of Forestry</t>
-        </is>
-      </c>
+          <t>Dr. Ir. Baharuddin, MP</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Management of Honey Bees and Beneficial Insects</t>
+          <t>Utilization of Non-Timber Forest Products</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -950,12 +942,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Ira Taskirawati S.Hut. M.Sc. Ph.D.</t>
+          <t>Andi Prastiyo, S.Hut., M.Hut.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -965,7 +957,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Forest Product Technology</t>
+          <t>Management of Honey Bees and Beneficial Insects</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -987,12 +979,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Putu Supadma Putra S.Hut</t>
+          <t>Ira Taskirawati S.Hut. M.Sc. Ph.D.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1002,7 +994,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Forest Ecology</t>
+          <t>Forest Product Technology</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1024,12 +1016,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Kidung Tirtayasa Putra Pangestu, S.Hut., M.Si.</t>
+          <t>Dr. Putu Supadma Putra S.Hut</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1039,7 +1031,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Engineered Cutting Tool, Computer Numerical Control Machine</t>
+          <t>Forest Ecology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1061,12 +1053,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. A. Detti Yunianti, S.Hut., MP</t>
+          <t>Dr. Kidung Tirtayasa Putra Pangestu, S.Hut., M.Si.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1076,7 +1068,7 @@
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Wood Anatomy; Wood Quality</t>
+          <t>Engineered Cutting Tool, Computer Numerical Control Machine</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,12 +1090,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Sri Rahayu Diza Lestari A, S.Hut., M.Si</t>
+          <t>Prof. Dr. A. Detti Yunianti, S.Hut., MP</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1113,7 +1105,7 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Biocomposite Technology</t>
+          <t>Wood Anatomy; Wood Quality</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1135,22 +1127,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Wan Mohd Nazri Wan Abdul Rahman</t>
+          <t>Dr. Andi Sri Rahayu Diza Lestari A, S.Hut., M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Universiti Teknologi MARA</t>
+          <t>Faculty of Forestry</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Wood Technology, Wood Utilisation</t>
+          <t>Biocomposite Technology</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1172,22 +1164,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Nur Abdi Aminullah</t>
+          <t>Prof. Dr. Wan Mohd Nazri Wan Abdul Rahman</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Faculty of Forestry</t>
+          <t>Universiti Teknologi MARA</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Utilization of Non-Timber Forest Products</t>
+          <t>Wood Technology, Wood Utilisation</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1209,12 +1201,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Lina Mangiwa</t>
+          <t>Nur Abdi Aminullah</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1224,7 +1216,7 @@
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Forest Concervation</t>
+          <t>Utilization of Non-Timber Forest Products</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1246,12 +1238,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin</t>
+          <t>Lina Mangiwa</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1261,7 +1253,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Utilization of Non-Timber Forest Products</t>
+          <t>Forest Concervation</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1283,12 +1275,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Wardiman Mas’ud, S.Hut, M.Si</t>
+          <t>Hasanuddin</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1298,7 +1290,7 @@
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Ecology</t>
+          <t>Utilization of Non-Timber Forest Products</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
@@ -1320,12 +1312,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Syahidah, S. Hut., M.Si, Ph.D.</t>
+          <t>Wardiman Mas’ud, S.Hut, M.Si</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1333,7 +1325,11 @@
           <t>Faculty of Forestry</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n"/>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Ecology</t>
+        </is>
+      </c>
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
@@ -1353,12 +1349,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Ira Taskirawati S.Hut. M.Sc. Ph.D.</t>
+          <t>Syahidah, S. Hut., M.Si, Ph.D.</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1366,11 +1362,7 @@
           <t>Faculty of Forestry</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Forest Product Technology</t>
-        </is>
-      </c>
+      <c r="E17" s="11" t="n"/>
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
@@ -1388,10 +1380,26 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Ira Taskirawati S.Hut. M.Sc. Ph.D.</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Faculty of Forestry</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Forest Product Technology</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1399,7 +1407,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1588,15 +1600,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_nifodi.xlsx
+++ b/forms/trg/Formulir_TRG_nifodi.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Ir. Baharuddin, MP</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
